--- a/simulations/correction_peat_market/AS_taux de tri/AS_resume-incin.xlsx
+++ b/simulations/correction_peat_market/AS_taux de tri/AS_resume-incin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS_taux de tri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3738C389-DDA4-4122-8552-EFB32ECB8AE4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F6266F-B09D-4F6A-BCBB-F66F3400446E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ss_inv_inc" sheetId="4" r:id="rId1"/>
@@ -5422,15 +5422,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5462,16 +5462,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>693737</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>153987</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>695325</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6805,6 +6805,9 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
+          <cell r="AK3">
+            <v>-651101.69874275697</v>
+          </cell>
           <cell r="AR3">
             <v>6.5</v>
           </cell>
